--- a/docs/samples/school_realistic.xlsx
+++ b/docs/samples/school_realistic.xlsx
@@ -707,7 +707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -721,6 +721,11 @@
           <t>name</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>department</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -733,6 +738,11 @@
           <t>GV1</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -745,6 +755,11 @@
           <t>GV2</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -757,6 +772,11 @@
           <t>GV3</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -769,6 +789,11 @@
           <t>GV4</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -781,6 +806,11 @@
           <t>GV5</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -793,6 +823,11 @@
           <t>GV6</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -805,6 +840,11 @@
           <t>GV7</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -817,6 +857,11 @@
           <t>GV8</t>
         </is>
       </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -829,6 +874,11 @@
           <t>GV9</t>
         </is>
       </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -841,6 +891,11 @@
           <t>GV10</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -853,6 +908,11 @@
           <t>GV11</t>
         </is>
       </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -865,6 +925,11 @@
           <t>GV12</t>
         </is>
       </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -877,6 +942,11 @@
           <t>GV13</t>
         </is>
       </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -889,6 +959,11 @@
           <t>GV14</t>
         </is>
       </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -901,6 +976,11 @@
           <t>GV15</t>
         </is>
       </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -913,6 +993,11 @@
           <t>GV16</t>
         </is>
       </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -925,6 +1010,11 @@
           <t>GV17</t>
         </is>
       </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -937,6 +1027,11 @@
           <t>GV18</t>
         </is>
       </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -949,6 +1044,11 @@
           <t>GV19</t>
         </is>
       </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -959,6 +1059,11 @@
       <c r="B21" t="inlineStr">
         <is>
           <t>GV20</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1249,7 +1354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1283,6 +1388,11 @@
           <t>required_room_type</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>department</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1302,7 +1412,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>GV11</t>
+          <t>GV1</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -1313,6 +1423,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1332,7 +1447,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>GV6</t>
+          <t>GV3</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -1343,6 +1458,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1362,7 +1482,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>GV7</t>
+          <t>GV4</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1373,6 +1493,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1392,7 +1517,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>GV8</t>
+          <t>GV5</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1403,6 +1528,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1422,7 +1552,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>GV9</t>
+          <t>GV20</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1433,6 +1563,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1452,7 +1587,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>GV4</t>
+          <t>GV16</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1463,6 +1598,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1482,7 +1622,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>GV12</t>
+          <t>GV2</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1493,6 +1633,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1512,7 +1657,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>GV6</t>
+          <t>GV3</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1523,6 +1668,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1542,7 +1692,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>GV7</t>
+          <t>GV4</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1553,6 +1703,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1572,7 +1727,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>GV8</t>
+          <t>GV5</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1583,6 +1738,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1602,7 +1762,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>GV9</t>
+          <t>GV20</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1613,6 +1773,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1632,7 +1797,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>GV5</t>
+          <t>GV17</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1643,6 +1808,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1662,7 +1832,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>GV11</t>
+          <t>GV8</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1673,6 +1843,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1692,7 +1867,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>GV12</t>
+          <t>GV9</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1703,6 +1878,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1722,7 +1902,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>GV14</t>
+          <t>GV10</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1733,6 +1913,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1752,7 +1937,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>GV15</t>
+          <t>GV6</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1763,6 +1948,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1782,7 +1972,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>GV13</t>
+          <t>GV16</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1793,6 +1983,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1812,7 +2007,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>GV1</t>
+          <t>GV20</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1823,6 +2018,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1842,7 +2042,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>GV13</t>
+          <t>GV8</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1853,6 +2053,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1872,7 +2077,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>GV16</t>
+          <t>GV9</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1883,6 +2088,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1902,7 +2112,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>GV17</t>
+          <t>GV7</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -1913,6 +2123,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1932,7 +2147,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>GV18</t>
+          <t>GV10</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1943,6 +2158,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1962,7 +2182,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>GV14</t>
+          <t>GV17</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1973,6 +2193,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1992,7 +2217,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>GV10</t>
+          <t>GV18</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -2003,6 +2228,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2022,7 +2252,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>GV19</t>
+          <t>GV8</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -2033,6 +2263,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2052,7 +2287,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>GV15</t>
+          <t>GV10</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -2063,6 +2298,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2082,7 +2322,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>GV2</t>
+          <t>GV9</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -2093,6 +2333,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2112,7 +2357,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>GV20</t>
+          <t>GV6</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -2123,6 +2368,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2142,7 +2392,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>GV3</t>
+          <t>GV16</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -2153,6 +2403,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2172,7 +2427,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>GV4</t>
+          <t>GV19</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -2183,6 +2438,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2202,7 +2462,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>GV4</t>
+          <t>GV7</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -2213,6 +2473,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2232,7 +2497,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>GV16</t>
+          <t>GV6</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -2243,6 +2508,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2262,7 +2532,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>GV5</t>
+          <t>GV8</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -2273,6 +2543,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2292,7 +2567,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>GV1</t>
+          <t>GV9</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -2303,6 +2578,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2322,7 +2602,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>GV10</t>
+          <t>GV17</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -2333,6 +2613,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2352,7 +2637,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>GV6</t>
+          <t>GV20</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -2363,6 +2648,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2382,7 +2672,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>GV17</t>
+          <t>GV7</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -2393,6 +2683,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2412,7 +2707,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>GV6</t>
+          <t>GV10</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -2423,6 +2718,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2442,7 +2742,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>GV7</t>
+          <t>GV6</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -2453,6 +2753,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2483,6 +2788,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2502,7 +2812,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>GV9</t>
+          <t>GV18</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -2513,6 +2823,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2532,7 +2847,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>GV5</t>
+          <t>GV16</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -2543,6 +2858,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2562,7 +2882,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>GV18</t>
+          <t>GV8</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -2573,6 +2893,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2592,7 +2917,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>GV11</t>
+          <t>GV7</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -2603,6 +2928,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2622,7 +2952,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>GV12</t>
+          <t>GV9</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -2633,6 +2963,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2652,7 +2987,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>GV13</t>
+          <t>GV10</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -2663,6 +2998,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2682,7 +3022,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>GV14</t>
+          <t>GV19</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -2693,6 +3033,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2712,7 +3057,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>GV7</t>
+          <t>GV17</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -2723,6 +3068,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2742,7 +3092,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>GV19</t>
+          <t>GV9</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -2753,6 +3103,11 @@
           <t>mba</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2772,7 +3127,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>GV2</t>
+          <t>GV10</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -2783,6 +3138,11 @@
           <t>mba</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2802,7 +3162,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>GV15</t>
+          <t>GV6</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -2813,6 +3173,11 @@
           <t>mba</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2832,7 +3197,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>GV16</t>
+          <t>GV7</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -2843,6 +3208,11 @@
           <t>mba</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2862,7 +3232,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>GV20</t>
+          <t>GV6</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -2873,6 +3243,11 @@
           <t>mba</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2892,7 +3267,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>GV3</t>
+          <t>GV7</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -2903,6 +3278,11 @@
           <t>mba</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2922,7 +3302,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>GV17</t>
+          <t>GV8</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -2933,6 +3313,11 @@
           <t>mba</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2952,7 +3337,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>GV18</t>
+          <t>GV9</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -2963,6 +3348,11 @@
           <t>mba</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2982,7 +3372,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>GV1</t>
+          <t>GV11</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -2993,6 +3383,11 @@
           <t>art</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3012,7 +3407,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>GV19</t>
+          <t>GV13</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -3023,6 +3418,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3042,7 +3442,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>GV2</t>
+          <t>GV14</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -3053,6 +3453,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3072,7 +3477,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>GV4</t>
+          <t>GV18</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -3083,6 +3488,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3102,7 +3512,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>GV8</t>
+          <t>GV19</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -3113,6 +3523,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3132,7 +3547,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>GV10</t>
+          <t>GV12</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -3143,6 +3558,11 @@
           <t>art</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3162,7 +3582,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>GV20</t>
+          <t>GV15</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -3173,6 +3593,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3192,7 +3617,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>GV3</t>
+          <t>GV13</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -3203,6 +3628,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3222,7 +3652,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>GV5</t>
+          <t>GV19</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -3233,6 +3663,11 @@
           <t>standard</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3252,7 +3687,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>GV9</t>
+          <t>GV18</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -3261,6 +3696,11 @@
       <c r="F67" t="inlineStr">
         <is>
           <t>standard</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3341,31 +3781,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sức chứa</t>
+          <t>Nhóm chuyên môn</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tạm đặt 30 cho mọi phòng, chờ số chính xác.</t>
+          <t>Cột department: giáo viên chỉ dạy môn cùng nhóm (IT, Business, Design, English).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G311 (loại khỏi bài toán)</t>
+          <t>Sức chứa</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hội trường, tổ chức sự kiện</t>
+          <t>Tạm đặt 30 cho mọi phòng, chờ số chính xác.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G312 (loại khỏi bài toán)</t>
+          <t>G311 (loại khỏi bài toán)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3377,70 +3817,82 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G315 (loại khỏi bài toán)</t>
+          <t>G312 (loại khỏi bài toán)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Phòng tư vấn tuyển sinh</t>
+          <t>Hội trường, tổ chức sự kiện</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G320 (loại khỏi bài toán)</t>
+          <t>G315 (loại khỏi bài toán)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Phòng để đồ, chưa có thông tin</t>
+          <t>Phòng tư vấn tuyển sinh</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G501 (loại khỏi bài toán)</t>
+          <t>G320 (loại khỏi bài toán)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Phòng Director</t>
+          <t>Phòng để đồ, chưa có thông tin</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G505 (loại khỏi bài toán)</t>
+          <t>G501 (loại khỏi bài toán)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Academic Affairs Administration Dept.</t>
+          <t>Phòng Director</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>G506 (loại khỏi bài toán)</t>
+          <t>G505 (loại khỏi bài toán)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Thư viện</t>
+          <t>Academic Affairs Administration Dept.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>G506 (loại khỏi bài toán)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Thư viện</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>G507 (loại khỏi bài toán)</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Student service</t>
         </is>
